--- a/dados/Gestores.xlsx
+++ b/dados/Gestores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1021328\Documents\ordem_servico\proposta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\42094727866\Desktop\Ordem_Servico\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6398992C-CE47-452C-936B-B106F9A1FCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FAD06F2-24F9-4674-AC73-8B50129F297D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1D263CFF-52C9-4ABA-BE0E-2439ECD4DC51}"/>
   </bookViews>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>Alex</t>
   </si>
@@ -104,29 +93,20 @@
     <t>cargo</t>
   </si>
   <si>
-    <t>OPP</t>
-  </si>
-  <si>
-    <t>Coord Ped</t>
-  </si>
-  <si>
-    <t>Coord Tec</t>
-  </si>
-  <si>
-    <t>Manut</t>
-  </si>
-  <si>
-    <t>Secret</t>
-  </si>
-  <si>
-    <t>Coord</t>
+    <t>Orientador de práticas profissionais</t>
+  </si>
+  <si>
+    <t>Coordenador Técnico</t>
+  </si>
+  <si>
+    <t>Coordenador Pedagógico</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,6 +127,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF21FF7D"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -184,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -196,6 +182,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,12 +521,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7A743F0-8479-4576-8284-7D370ECE8B00}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -548,118 +537,118 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15">
       <c r="A8" s="5">
         <v>1015370</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15">
       <c r="A10" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>27</v>
+      <c r="C11" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
+  <sortState ref="A2:B11">
     <sortCondition ref="B2:B11"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
